--- a/data/trans_dic/IP44C$ninguna_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que no han tenido retrasos en pagos</t>
+          <t>Adultos que no han tenido retrasos en pagos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,12; 87,36</t>
+          <t>72,27; 87,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,29; 91,74</t>
+          <t>78,2; 91,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,34; 87,77</t>
+          <t>77,38; 87,92</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,25; 88,54</t>
+          <t>79,2; 88,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,26; 83,56</t>
+          <t>73,04; 83,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,64; 84,68</t>
+          <t>77,67; 84,77</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,23; 86,61</t>
+          <t>74,81; 86,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,9; 91,7</t>
+          <t>83,38; 91,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81,47; 88,34</t>
+          <t>80,44; 88,01</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>55,9; 90,13</t>
+          <t>56,38; 90,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,71; 90,6</t>
+          <t>83,21; 90,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,25; 89,03</t>
+          <t>70,17; 88,87</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>69,67; 85,76</t>
+          <t>69,35; 85,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,95; 87,47</t>
+          <t>82,9; 87,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,11; 85,81</t>
+          <t>77,02; 85,75</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que no han tenido retrasos en pagos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>45898</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52420</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>98318</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>41171; 49588</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>47754; 55786</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>91340; 103771</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>131335</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>140395</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>271730</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>123487; 137726</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>130079; 148843</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>259449; 283153</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>138237</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>179161</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>317399</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>127201; 147471</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>169750; 187055</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>300523; 328832</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>215605</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>263186</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>478791</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>151767; 242535</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>250706; 273833</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>400296; 506995</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1591</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>531074</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>635163</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1166237</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>452247; 560631</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>616796; 652291</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1075361; 1197165</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$ninguna_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,27; 87,04</t>
+          <t>72,4; 87,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,2; 91,36</t>
+          <t>77,6; 91,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,38; 87,92</t>
+          <t>77,74; 87,74</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,2; 88,33</t>
+          <t>79,03; 88,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,04; 83,58</t>
+          <t>73,12; 83,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,67; 84,77</t>
+          <t>77,61; 84,62</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,81; 86,73</t>
+          <t>74,22; 86,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,38; 91,88</t>
+          <t>83,35; 91,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,44; 88,01</t>
+          <t>80,97; 88,47</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56,38; 90,1</t>
+          <t>55,97; 90,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,21; 90,88</t>
+          <t>82,91; 90,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,17; 88,87</t>
+          <t>70,99; 88,88</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>69,35; 85,97</t>
+          <t>65,74; 85,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,9; 87,67</t>
+          <t>82,89; 87,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,02; 85,75</t>
+          <t>77,74; 85,92</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41171; 49588</t>
+          <t>41246; 49652</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47754; 55786</t>
+          <t>47386; 55743</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91340; 103771</t>
+          <t>91760; 103568</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>123487; 137726</t>
+          <t>123231; 137796</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>130079; 148843</t>
+          <t>130228; 149207</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>259449; 283153</t>
+          <t>259230; 282639</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>127201; 147471</t>
+          <t>126193; 147009</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>169750; 187055</t>
+          <t>169687; 187176</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>300523; 328832</t>
+          <t>302531; 330542</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>151767; 242535</t>
+          <t>150662; 242699</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>250706; 273833</t>
+          <t>249826; 273908</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>400296; 506995</t>
+          <t>405017; 507046</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>452247; 560631</t>
+          <t>428690; 559367</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>616796; 652291</t>
+          <t>616709; 652008</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1075361; 1197165</t>
+          <t>1085398; 1199550</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$ninguna_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,01%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72,4; 87,15</t>
+          <t>77,19; 91,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>77,6; 91,29</t>
+          <t>72,54; 87,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,74; 87,74</t>
+          <t>76,88; 87,49</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,03; 88,37</t>
+          <t>73,11; 83,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,12; 83,78</t>
+          <t>78,58; 88,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,61; 84,62</t>
+          <t>77,57; 84,52</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,22; 86,46</t>
+          <t>81,51; 90,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,35; 91,94</t>
+          <t>75,84; 86,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,97; 88,47</t>
+          <t>81,62; 88,24</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>86,84%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>55,97; 90,16</t>
+          <t>81,96; 89,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,91; 90,91</t>
+          <t>82,49; 90,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,99; 88,88</t>
+          <t>84,0; 89,51</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>65,74; 85,78</t>
+          <t>82,46; 87,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,89; 87,63</t>
+          <t>81,19; 86,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,74; 85,92</t>
+          <t>82,7; 86,26</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>87</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45898</t>
+          <t>42772</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52420</t>
+          <t>41764</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98318</t>
+          <t>84536</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41246; 49652</t>
+          <t>38767; 45907</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47386; 55743</t>
+          <t>37438; 45226</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91760; 103568</t>
+          <t>78286; 89091</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>210</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>131335</t>
+          <t>120659</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>140395</t>
+          <t>120160</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>271730</t>
+          <t>240819</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>123231; 137796</t>
+          <t>111787; 127858</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>130228; 149207</t>
+          <t>112664; 126334</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>259230; 282639</t>
+          <t>229823; 250433</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>191</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>138237</t>
+          <t>166883</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>179161</t>
+          <t>140779</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317399</t>
+          <t>307660</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>126193; 147009</t>
+          <t>156165; 174322</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>169687; 187176</t>
+          <t>130018; 148663</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>302531; 330542</t>
+          <t>296308; 320327</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>296</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>215605</t>
+          <t>249535</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>263186</t>
+          <t>218404</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>478791</t>
+          <t>467939</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>150662; 242699</t>
+          <t>236339; 259288</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>249826; 273908</t>
+          <t>206618; 227558</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>405017; 507046</t>
+          <t>452610; 482321</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>784</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>807</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>531074</t>
+          <t>579849</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>635163</t>
+          <t>521106</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1166237</t>
+          <t>1100955</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>428690; 559367</t>
+          <t>563302; 595555</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>616709; 652008</t>
+          <t>500868; 534917</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1085398; 1199550</t>
+          <t>1075138; 1121333</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$ninguna_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que no han tenido retrasos en pagos (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>85,16%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>80,92%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>83,01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>77,19; 91,4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>72,54; 87,63</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>76,88; 87,49</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>78,91%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>83,8%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>81,28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>73,11; 83,62</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>78,58; 88,11</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>77,57; 84,52</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>87,1%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>82,12%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>84,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>81,51; 90,99</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>75,84; 86,72</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>81,62; 88,24</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>86,54%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>87,19%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>86,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>81,96; 89,92</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>82,49; 90,85</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>84,0; 89,51</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>84,89%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>84,47%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>84,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>82,46; 87,19</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>81,19; 86,71</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>82,7; 86,26</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.8516281757770432</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.8091977424365578</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.8301240196568036</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>42772</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>41764</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>84536</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.7718795540305006</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.7253975722253428</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.7687508862933484</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>38767; 45907</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>37438; 45226</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>78286; 89091</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.914039873843455</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.8762914417349109</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.8748557361081621</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.7890967403622463</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.8380481220357979</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.8127854350086304</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>120659</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>120160</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>240819</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.7310744226922614</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.7857647117651829</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.7756732803193457</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>111787; 127858</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>112664; 126334</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>229823; 250433</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.8361761068869275</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.8811078809023545</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.8452310610984923</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.8710307005804389</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.8211873458679301</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.8474929325781717</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>166883</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>140779</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>307660</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.8150889364703646</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.7584185380258732</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.8162206617457364</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>156165; 174322</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>130018; 148663</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>296308; 320327</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9098598699293631</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.8671812214855437</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.8823854951657347</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8653540232793081</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.871940199554383</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8684155950449403</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>249535</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>218404</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>467939</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8195897245541174</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.8248866526852869</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.8399687116301601</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>236339; 259288</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>206618; 227558</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>452610; 482321</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.8991766201439906</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9084873628533366</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.8951066174251546</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>807</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1591</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.8488669378034289</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.8447100853252083</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.8468943225906154</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>579849</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>521106</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1100955</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8246427522928514</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.8119040574921438</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.8270347586994315</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>563302; 595555</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>500868; 534917</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1075138; 1121333</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.8718596627219037</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.8670979684719515</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.8625700402158752</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que no han tenido retrasos en pagos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>42772</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>41764</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>84536</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>38767</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>37438</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>78286</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>45907</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>45226</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>89091</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>212</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>120659</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>120160</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>240819</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>111787</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>112664</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>229823</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>127858</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>126334</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>250433</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>206</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>191</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>166883</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>140779</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>307660</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>156165</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>130018</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>296308</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>174322</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>148663</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>320327</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>291</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>296</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>249535</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>218404</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>467939</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>236339</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>206618</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>452610</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>259288</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>227558</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>482321</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>807</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>784</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>579849</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>521106</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1100955</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>563302</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>500868</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1075138</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>595555</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>534917</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1121333</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>